--- a/Data_clean/MCAS/Estados_US/Edos_USA_2015/MASSACHUSETTS_2015.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2015/MASSACHUSETTS_2015.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D362"/>
+  <dimension ref="A1:D356"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Total</t>
@@ -470,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -501,9 +521,14 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amatenango de la Frontera</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C10">
@@ -514,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Arriaga</t>
@@ -527,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Cacahoatán</t>
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Chamula</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Chapultenango</t>
@@ -566,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Chicomuselo</t>
@@ -579,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>El Porvenir</t>
@@ -592,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Escuintla</t>
@@ -605,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -618,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Frontera Hidalgo</t>
@@ -631,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -644,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Huixtán</t>
@@ -657,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Huixtla</t>
@@ -670,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Jiquipilas</t>
@@ -683,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -696,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -709,9 +809,14 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mazapa de Madero</t>
+          <t>Mazapa De Madero</t>
         </is>
       </c>
       <c r="C26">
@@ -722,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -735,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Ocosingo</t>
@@ -748,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Palenque</t>
@@ -761,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Pantelhó</t>
@@ -774,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Pichucalco</t>
@@ -787,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Sabanilla</t>
@@ -800,9 +935,14 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>San Cristóbal de las Casas</t>
+          <t>San Cristóbal De Las Casas</t>
         </is>
       </c>
       <c r="C33">
@@ -813,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Siltepec</t>
@@ -826,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -839,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Tenejapa</t>
@@ -852,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Tumbalá</t>
@@ -865,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Tuxtla Chico</t>
@@ -878,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Tzimol</t>
@@ -891,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Unión Juárez</t>
@@ -904,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Villa Comaltitlán</t>
@@ -917,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Total</t>
@@ -948,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Total</t>
@@ -979,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1010,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1025,7 +1225,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1041,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -1054,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1067,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -1080,9 +1295,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cuajimalpa de Morelos</t>
+          <t>Cuajimalpa De Morelos</t>
         </is>
       </c>
       <c r="C53">
@@ -1093,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1106,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -1119,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -1132,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1145,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1158,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Milpa Alta</t>
@@ -1171,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -1184,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1197,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1228,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Durango</t>
@@ -1241,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -1254,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Lerdo</t>
@@ -1267,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Poanas</t>
@@ -1280,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>San Dimas</t>
@@ -1293,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1308,12 +1603,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Acambay de Ruíz Castañeda</t>
+          <t>Acambay De Ruíz Castañeda</t>
         </is>
       </c>
       <c r="C70">
@@ -1324,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Aculco</t>
@@ -1337,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Amatepec</t>
@@ -1350,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Atlacomulco</t>
@@ -1363,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Chicoloapan</t>
@@ -1376,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Chimalhuacán</t>
@@ -1389,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Coatepec Harinas</t>
@@ -1402,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Cuautitlán</t>
@@ -1415,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C78">
@@ -1428,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Jilotepec</t>
@@ -1441,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C80">
@@ -1454,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -1467,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Nicolás Romero</t>
@@ -1480,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Tecámac</t>
@@ -1493,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Temascalcingo</t>
@@ -1506,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Teoloyucan</t>
@@ -1519,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Teotihuacán</t>
@@ -1532,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C87">
@@ -1545,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -1558,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -1571,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Zumpango</t>
@@ -1584,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1604,7 +2004,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C92">
@@ -1615,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -1628,9 +2033,14 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna de la Independencia Nacional</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C94">
@@ -1641,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -1654,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Jerécuaro</t>
@@ -1667,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>León</t>
@@ -1680,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -1693,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -1706,9 +2141,14 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Santa Cruz de Juventino Rosas</t>
+          <t>Santa Cruz De Juventino Rosas</t>
         </is>
       </c>
       <c r="C100">
@@ -1719,9 +2159,14 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Silao de la Victoria</t>
+          <t>Silao De La Victoria</t>
         </is>
       </c>
       <c r="C101">
@@ -1732,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -1745,9 +2195,14 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Valle de Santiago</t>
+          <t>Valle De Santiago</t>
         </is>
       </c>
       <c r="C103">
@@ -1758,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Xichú</t>
@@ -1771,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1791,7 +2256,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C106">
@@ -1802,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Ahuacuotzingo</t>
@@ -1815,9 +2285,14 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Alcozauca de Guerrero</t>
+          <t>Alcozauca De Guerrero</t>
         </is>
       </c>
       <c r="C108">
@@ -1828,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Arcelia</t>
@@ -1841,9 +2321,14 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C110">
@@ -1854,9 +2339,14 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C111">
@@ -1867,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Copala</t>
@@ -1880,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Copanatoyac</t>
@@ -1893,9 +2393,14 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C114">
@@ -1906,9 +2411,14 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Coyuca de Catalán</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C115">
@@ -1919,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Cuajinicuilapa</t>
@@ -1932,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Eduardo Neri</t>
@@ -1945,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>General Heliodoro Castillo</t>
@@ -1958,9 +2483,14 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Iguala de la Independencia</t>
+          <t>Iguala De La Independencia</t>
         </is>
       </c>
       <c r="C119">
@@ -1971,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Malinaltepec</t>
@@ -1984,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Olinalá</t>
@@ -1997,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -2010,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>San Miguel Totolapan</t>
@@ -2023,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Tecoanapa</t>
@@ -2036,9 +2591,14 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Tepecoacuilco de Trujano</t>
+          <t>Tepecoacuilco De Trujano</t>
         </is>
       </c>
       <c r="C125">
@@ -2049,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Tlacoapa</t>
@@ -2062,9 +2627,14 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C127">
@@ -2075,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Xalpatláhuac</t>
@@ -2088,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Zirándaro</t>
@@ -2101,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2132,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Alfajayucan</t>
@@ -2145,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Chapantongo</t>
@@ -2158,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Chapulhuacán</t>
@@ -2171,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Francisco I. Madero</t>
@@ -2184,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -2197,9 +2807,14 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Jacala de Ledezma</t>
+          <t>Jacala De Ledezma</t>
         </is>
       </c>
       <c r="C137">
@@ -2210,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Metztitlán</t>
@@ -2223,9 +2843,14 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C139">
@@ -2236,9 +2861,14 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Progreso de Obregón</t>
+          <t>Progreso De Obregón</t>
         </is>
       </c>
       <c r="C140">
@@ -2249,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Tecozautla</t>
@@ -2262,9 +2897,14 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Tenango de Doria</t>
+          <t>Tenango De Doria</t>
         </is>
       </c>
       <c r="C142">
@@ -2275,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Tlahuiltepa</t>
@@ -2288,9 +2933,14 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Tula de Allende</t>
+          <t>Tula De Allende</t>
         </is>
       </c>
       <c r="C144">
@@ -2301,9 +2951,14 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C145">
@@ -2314,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2345,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Cihuatlán</t>
@@ -2358,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Ejutla</t>
@@ -2371,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -2384,6 +3059,11 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Jalostotitlán</t>
@@ -2397,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -2410,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>La Barca</t>
@@ -2423,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>La Huerta</t>
@@ -2436,9 +3131,14 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>La Manzanilla de la Paz</t>
+          <t>La Manzanilla De La Paz</t>
         </is>
       </c>
       <c r="C155">
@@ -2449,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Magdalena</t>
@@ -2462,9 +3167,14 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Ojuelos de Jalisco</t>
+          <t>Ojuelos De Jalisco</t>
         </is>
       </c>
       <c r="C157">
@@ -2475,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -2488,6 +3203,11 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -2501,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Tecalitlán</t>
@@ -2514,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -2527,9 +3257,14 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Teocuitatlán de Corona</t>
+          <t>Teocuitatlán De Corona</t>
         </is>
       </c>
       <c r="C162">
@@ -2540,9 +3275,14 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Tizapán el Alto</t>
+          <t>Tizapán El Alto</t>
         </is>
       </c>
       <c r="C163">
@@ -2553,9 +3293,14 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Tlajomulco de Zúñiga</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C164">
@@ -2566,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>San Pedro Tlaquepaque</t>
@@ -2579,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Tuxcueca</t>
@@ -2592,9 +3347,14 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C167">
@@ -2605,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -2618,6 +3383,11 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2649,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Gabriel Zamora</t>
@@ -2662,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Huiramba</t>
@@ -2675,6 +3455,11 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -2688,6 +3473,11 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Lagunillas</t>
@@ -2701,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -2714,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Pajacuarán</t>
@@ -2727,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Pátzcuaro</t>
@@ -2740,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>Quiroga</t>
@@ -2753,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Salvador Escalante</t>
@@ -2766,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -2779,6 +3599,11 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -2792,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2823,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -2836,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -2849,6 +3689,11 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>Jantetelco</t>
@@ -2862,6 +3707,11 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Ocuituco</t>
@@ -2875,9 +3725,14 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Puente de Ixtla</t>
+          <t>Puente De Ixtla</t>
         </is>
       </c>
       <c r="C188">
@@ -2888,9 +3743,14 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Tetela del Volcán</t>
+          <t>Tetela Del Volcán</t>
         </is>
       </c>
       <c r="C189">
@@ -2901,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Yautepec</t>
@@ -2914,6 +3779,11 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>Yecapixtla</t>
@@ -2927,6 +3797,11 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2958,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>San Blas</t>
@@ -2971,6 +3851,11 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>Tecuala</t>
@@ -2984,6 +3869,11 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -2997,6 +3887,11 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -3010,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3041,6 +3941,11 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -3054,6 +3959,11 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3074,7 +3984,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Acatlán de Pérez Figueroa</t>
+          <t>Acatlán De Pérez Figueroa</t>
         </is>
       </c>
       <c r="C202">
@@ -3085,6 +3995,11 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>Coatecas Altas</t>
@@ -3098,9 +4013,14 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Coicoyán de las Flores</t>
+          <t>Coicoyán De Las Flores</t>
         </is>
       </c>
       <c r="C204">
@@ -3111,9 +4031,14 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Ixtlán de Juárez</t>
+          <t>Ixtlán De Juárez</t>
         </is>
       </c>
       <c r="C205">
@@ -3124,9 +4049,14 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C206">
@@ -3137,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Matías Romero Avendaño</t>
@@ -3150,9 +4085,14 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C208">
@@ -3163,9 +4103,14 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Pinotepa de Don Luis</t>
+          <t>Pinotepa De Don Luis</t>
         </is>
       </c>
       <c r="C209">
@@ -3176,9 +4121,14 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerrero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C210">
@@ -3189,6 +4139,11 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>San Agustín Yatareni</t>
@@ -3202,6 +4157,11 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>San Antonino Monte Verde</t>
@@ -3215,6 +4175,11 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>San Antonio Huitepec</t>
@@ -3228,6 +4193,11 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>San Carlos Yautepec</t>
@@ -3241,6 +4211,11 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -3254,6 +4229,11 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>San Martín Peras</t>
@@ -3267,6 +4247,11 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>San Miguel Panixtlahuaca</t>
@@ -3280,6 +4265,11 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>San Pedro Pochutla</t>
@@ -3293,9 +4283,14 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>San Pedro y San Pablo Teposcolula</t>
+          <t>San Pedro Y San Pablo Teposcolula</t>
         </is>
       </c>
       <c r="C219">
@@ -3306,6 +4301,11 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>San Sebastián Coatlán</t>
@@ -3319,6 +4319,11 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>Santa Catarina Juquila</t>
@@ -3332,6 +4337,11 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Santa Cruz Zenzontepec</t>
@@ -3345,6 +4355,11 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
           <t>Santiago Huajolotitlán</t>
@@ -3358,6 +4373,11 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Santiago Pinotepa Nacional</t>
@@ -3371,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>Santiago Zacatepec</t>
@@ -3384,6 +4409,11 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>Santo Domingo Tepuxtepec</t>
@@ -3397,9 +4427,14 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Tlacolula de Matamoros</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C227">
@@ -3410,9 +4445,14 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Totontepec Villa de Morelos</t>
+          <t>Totontepec Villa De Morelos</t>
         </is>
       </c>
       <c r="C228">
@@ -3423,9 +4463,14 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Villa de Etla</t>
+          <t>Villa De Etla</t>
         </is>
       </c>
       <c r="C229">
@@ -3436,9 +4481,14 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Villa Talea de Castro</t>
+          <t>Villa Talea De Castro</t>
         </is>
       </c>
       <c r="C230">
@@ -3449,9 +4499,14 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Zimatlán de Álvarez</t>
+          <t>Zimatlán De Álvarez</t>
         </is>
       </c>
       <c r="C231">
@@ -3462,6 +4517,11 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3493,6 +4553,11 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>Acatlán</t>
@@ -3506,6 +4571,11 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>Ajalpan</t>
@@ -3519,6 +4589,11 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -3532,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>Atzitzihuacán</t>
@@ -3545,6 +4625,11 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
           <t>Caltepec</t>
@@ -3558,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>Chiautzingo</t>
@@ -3571,6 +4661,11 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>Chietla</t>
@@ -3584,6 +4679,11 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>Chignahuapan</t>
@@ -3597,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>Coronango</t>
@@ -3610,9 +4715,14 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Cuayuca de Andrade</t>
+          <t>Cuayuca De Andrade</t>
         </is>
       </c>
       <c r="C243">
@@ -3623,6 +4733,11 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>Esperanza</t>
@@ -3636,6 +4751,11 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -3649,6 +4769,11 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>Huejotzingo</t>
@@ -3662,9 +4787,14 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C247">
@@ -3675,6 +4805,11 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>Jolalpan</t>
@@ -3688,9 +4823,14 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Los Reyes de Juárez</t>
+          <t>Los Reyes De Juárez</t>
         </is>
       </c>
       <c r="C249">
@@ -3701,6 +4841,11 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>Nealtican</t>
@@ -3714,6 +4859,11 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -3727,6 +4877,11 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>San Andrés Cholula</t>
@@ -3740,6 +4895,11 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>San Jerónimo Tecuanipan</t>
@@ -3753,6 +4913,11 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>San José Miahuatlán</t>
@@ -3766,6 +4931,11 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>San Martín Texmelucan</t>
@@ -3779,6 +4949,11 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -3792,9 +4967,14 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>San Salvador el Verde</t>
+          <t>San Salvador El Verde</t>
         </is>
       </c>
       <c r="C257">
@@ -3805,6 +4985,11 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>Santa Isabel Cholula</t>
@@ -3818,9 +5003,14 @@
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Tecali de Herrera</t>
+          <t>Tecali De Herrera</t>
         </is>
       </c>
       <c r="C259">
@@ -3831,6 +5021,11 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -3844,6 +5039,11 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>Tepeojuma</t>
@@ -3857,6 +5057,11 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>Tepexco</t>
@@ -3870,9 +5075,14 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Tetela de Ocampo</t>
+          <t>Tetela De Ocampo</t>
         </is>
       </c>
       <c r="C263">
@@ -3883,6 +5093,11 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>Tlahuapan</t>
@@ -3896,6 +5111,11 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>Tlaola</t>
@@ -3909,6 +5129,11 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>Tlaxco</t>
@@ -3922,6 +5147,11 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
           <t>Tochimilco</t>
@@ -3935,6 +5165,11 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
           <t>Yehualtepec</t>
@@ -3948,6 +5183,11 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
           <t>Zacapoaxtla</t>
@@ -3961,6 +5201,11 @@
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3992,9 +5237,14 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Pinal de Amoles</t>
+          <t>Pinal De Amoles</t>
         </is>
       </c>
       <c r="C272">
@@ -4005,6 +5255,11 @@
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4036,6 +5291,11 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4067,6 +5327,11 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
           <t>Cárdenas</t>
@@ -4080,6 +5345,11 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
           <t>Cerritos</t>
@@ -4093,6 +5363,11 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -4106,6 +5381,11 @@
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
           <t>Salinas</t>
@@ -4119,6 +5399,11 @@
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -4132,6 +5417,11 @@
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
           <t>San Vicente Tancuayalab</t>
@@ -4145,6 +5435,11 @@
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
           <t>Santo Domingo</t>
@@ -4158,6 +5453,11 @@
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
           <t>Tamazunchale</t>
@@ -4171,6 +5471,11 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
           <t>Vanegas</t>
@@ -4184,9 +5489,14 @@
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Villa de Reyes</t>
+          <t>Villa De Reyes</t>
         </is>
       </c>
       <c r="C286">
@@ -4197,6 +5507,11 @@
       </c>
     </row>
     <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4228,6 +5543,11 @@
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -4241,6 +5561,11 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
           <t>Guasave</t>
@@ -4254,6 +5579,11 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
           <t>Mazatlán</t>
@@ -4267,6 +5597,11 @@
       </c>
     </row>
     <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4298,6 +5633,11 @@
       </c>
     </row>
     <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
           <t>Hermosillo</t>
@@ -4311,6 +5651,11 @@
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>Navojoa</t>
@@ -4324,6 +5669,11 @@
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
           <t>San Luis Río Colorado</t>
@@ -4337,6 +5687,11 @@
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4368,6 +5723,11 @@
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
           <t>Centro</t>
@@ -4381,6 +5741,11 @@
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
           <t>Comalcalco</t>
@@ -4394,6 +5759,11 @@
       </c>
     </row>
     <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
           <t>Cunduacán</t>
@@ -4407,6 +5777,11 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
           <t>Huimanguillo</t>
@@ -4420,6 +5795,11 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
           <t>Tenosique</t>
@@ -4433,6 +5813,11 @@
       </c>
     </row>
     <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4464,6 +5849,11 @@
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
           <t>El Mante</t>
@@ -4477,6 +5867,11 @@
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
           <t>Nuevo Laredo</t>
@@ -4490,6 +5885,11 @@
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -4503,6 +5903,11 @@
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -4516,6 +5921,11 @@
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
           <t>Valle Hermoso</t>
@@ -4529,6 +5939,11 @@
       </c>
     </row>
     <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4560,6 +5975,11 @@
       </c>
     </row>
     <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
           <t>Chiautempan</t>
@@ -4573,6 +5993,11 @@
       </c>
     </row>
     <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -4586,6 +6011,11 @@
       </c>
     </row>
     <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4617,9 +6047,14 @@
       </c>
     </row>
     <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Castillo de Teayo</t>
+          <t>Castillo De Teayo</t>
         </is>
       </c>
       <c r="C317">
@@ -4630,6 +6065,11 @@
       </c>
     </row>
     <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
           <t>Chacaltianguis</t>
@@ -4643,6 +6083,11 @@
       </c>
     </row>
     <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
           <t>Coatzacoalcos</t>
@@ -4656,6 +6101,11 @@
       </c>
     </row>
     <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -4669,9 +6119,14 @@
       </c>
     </row>
     <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Cosamaloapan de Carpio</t>
+          <t>Cosamaloapan De Carpio</t>
         </is>
       </c>
       <c r="C321">
@@ -4682,6 +6137,11 @@
       </c>
     </row>
     <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
           <t>Coscomatepec</t>
@@ -4695,6 +6155,11 @@
       </c>
     </row>
     <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr">
         <is>
           <t>Cosoleacaque</t>
@@ -4708,6 +6173,11 @@
       </c>
     </row>
     <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr">
         <is>
           <t>Espinal</t>
@@ -4721,6 +6191,11 @@
       </c>
     </row>
     <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -4734,9 +6209,14 @@
       </c>
     </row>
     <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Hueyapan de Ocampo</t>
+          <t>Hueyapan De Ocampo</t>
         </is>
       </c>
       <c r="C326">
@@ -4747,9 +6227,14 @@
       </c>
     </row>
     <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C327">
@@ -4760,6 +6245,11 @@
       </c>
     </row>
     <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B328" t="inlineStr">
         <is>
           <t>Ilamatlán</t>
@@ -4773,9 +6263,14 @@
       </c>
     </row>
     <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Ixhuatlán de Madero</t>
+          <t>Ixhuatlán De Madero</t>
         </is>
       </c>
       <c r="C329">
@@ -4786,6 +6281,11 @@
       </c>
     </row>
     <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
           <t>Ixtaczoquitlán</t>
@@ -4799,6 +6299,11 @@
       </c>
     </row>
     <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B331" t="inlineStr">
         <is>
           <t>Jáltipan</t>
@@ -4812,6 +6317,11 @@
       </c>
     </row>
     <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B332" t="inlineStr">
         <is>
           <t>José Azueta</t>
@@ -4825,6 +6335,11 @@
       </c>
     </row>
     <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B333" t="inlineStr">
         <is>
           <t>Juan Rodríguez Clara</t>
@@ -4838,6 +6353,11 @@
       </c>
     </row>
     <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B334" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -4851,9 +6371,14 @@
       </c>
     </row>
     <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C335">
@@ -4864,6 +6389,11 @@
       </c>
     </row>
     <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B336" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -4877,6 +6407,11 @@
       </c>
     </row>
     <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B337" t="inlineStr">
         <is>
           <t>Moloacán</t>
@@ -4890,6 +6425,11 @@
       </c>
     </row>
     <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B338" t="inlineStr">
         <is>
           <t>Nautla</t>
@@ -4903,6 +6443,11 @@
       </c>
     </row>
     <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B339" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -4916,6 +6461,11 @@
       </c>
     </row>
     <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B340" t="inlineStr">
         <is>
           <t>Papantla</t>
@@ -4929,6 +6479,11 @@
       </c>
     </row>
     <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -4942,9 +6497,14 @@
       </c>
     </row>
     <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Poza Rica de Hidalgo</t>
+          <t>Poza Rica De Hidalgo</t>
         </is>
       </c>
       <c r="C342">
@@ -4955,6 +6515,11 @@
       </c>
     </row>
     <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B343" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -4968,6 +6533,11 @@
       </c>
     </row>
     <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B344" t="inlineStr">
         <is>
           <t>San Juan Evangelista</t>
@@ -4981,6 +6551,11 @@
       </c>
     </row>
     <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B345" t="inlineStr">
         <is>
           <t>Tecolutla</t>
@@ -4994,6 +6569,11 @@
       </c>
     </row>
     <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B346" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -5007,6 +6587,11 @@
       </c>
     </row>
     <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B347" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -5020,6 +6605,11 @@
       </c>
     </row>
     <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B348" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -5033,6 +6623,11 @@
       </c>
     </row>
     <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B349" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -5046,6 +6641,11 @@
       </c>
     </row>
     <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B350" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5077,6 +6677,11 @@
       </c>
     </row>
     <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B352" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5108,9 +6713,14 @@
       </c>
     </row>
     <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Nochistlán de Mejía</t>
+          <t>Nochistlán De Mejía</t>
         </is>
       </c>
       <c r="C354">
@@ -5121,6 +6731,11 @@
       </c>
     </row>
     <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B355" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5144,41 +6759,6 @@
       </c>
       <c r="D356">
         <v>1</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
